--- a/content/post/drafts/weekly-picks/2025Lillehammer/men-points.xlsx
+++ b/content/post/drafts/weekly-picks/2025Lillehammer/men-points.xlsx
@@ -569,31 +569,31 @@
     <t xml:space="preserve">41.5090258592009</t>
   </si>
   <si>
+    <t xml:space="preserve">Arsi Ruuskanen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2866398581528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60548547815242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8921253363053</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jules Chappaz</t>
   </si>
   <si>
     <t xml:space="preserve">28.8974054211142</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98013378786954</t>
+    <t xml:space="preserve">8.96678768910737</t>
   </si>
   <si>
     <t xml:space="preserve">2.08715676943059</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9646959784143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arsi Ruuskanen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2866398581528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60548547815242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.8921253363053</t>
+    <t xml:space="preserve">39.9513498796522</t>
   </si>
   <si>
     <t xml:space="preserve">Anian Sossau</t>
@@ -749,6 +749,18 @@
     <t xml:space="preserve">27.5256946320645</t>
   </si>
   <si>
+    <t xml:space="preserve">Olivier Leveille</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3580506938451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4192967654913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7773474593364</t>
+  </si>
+  <si>
     <t xml:space="preserve">Håvard Moseby</t>
   </si>
   <si>
@@ -785,18 +797,6 @@
     <t xml:space="preserve">26.0532942291829</t>
   </si>
   <si>
-    <t xml:space="preserve">Olivier Leveille</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3580506938451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10656162148988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.464612315335</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sivert Wiig</t>
   </si>
   <si>
@@ -1004,6 +1004,12 @@
     <t xml:space="preserve">6.37029790654521</t>
   </si>
   <si>
+    <t xml:space="preserve">Emil Liekari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04584118621569</t>
+  </si>
+  <si>
     <t xml:space="preserve">Xavier McKeever</t>
   </si>
   <si>
@@ -1013,16 +1019,10 @@
     <t xml:space="preserve">1.77826920034807</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00369614099583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14699580568052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emil Liekari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04584118621569</t>
+    <t xml:space="preserve">2.42836446168712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57166412637182</t>
   </si>
   <si>
     <t xml:space="preserve">Matyas Bauer</t>
@@ -1082,16 +1082,16 @@
     <t xml:space="preserve">1.97497970291629</t>
   </si>
   <si>
+    <t xml:space="preserve">Miha Licef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57163045513154</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jiri Tuz</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71196299821339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miha Licef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57163045513154</t>
+    <t xml:space="preserve">1.55807202131444</t>
   </si>
   <si>
     <t xml:space="preserve">Eero Rantala</t>
@@ -1109,30 +1109,30 @@
     <t xml:space="preserve">Daito YAMAZAKI</t>
   </si>
   <si>
+    <t xml:space="preserve">Fredrik FODSTAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sebastian ENDRESTAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einar HEDEGART</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sander HAUKVIK-JENSEN</t>
   </si>
   <si>
-    <t xml:space="preserve">Einar HEDEGART</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ole Tafjord SUHRKE</t>
   </si>
   <si>
-    <t xml:space="preserve">Fredrik FODSTAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sebastian ENDRESTAD</t>
-  </si>
-  <si>
     <t xml:space="preserve">Einar Hedegart</t>
   </si>
   <si>
+    <t xml:space="preserve">Sander Haukvik Jensen</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ole Tafjord Suhrke</t>
   </si>
   <si>
-    <t xml:space="preserve">Sander Haukvik Jensen</t>
-  </si>
-  <si>
     <t xml:space="preserve">Michael Earnhart</t>
   </si>
   <si>
@@ -1160,19 +1160,19 @@
     <t xml:space="preserve">South Korea</t>
   </si>
   <si>
+    <t xml:space="preserve">Niks Saulitis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latvia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jong-Won Jeong</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oleksandr Lisohor</t>
   </si>
   <si>
     <t xml:space="preserve">Ukraine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niks Saulitis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latvia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jong-Won Jeong</t>
   </si>
   <si>
     <t xml:space="preserve">Bentley Walker-Broose</t>
@@ -2320,7 +2320,7 @@
         <v>16</v>
       </c>
       <c r="F27" t="n">
-        <v>0.140598576859704</v>
+        <v>0.0766185991760893</v>
       </c>
       <c r="G27" t="s">
         <v>125</v>
@@ -2407,7 +2407,7 @@
         <v>16</v>
       </c>
       <c r="F30" t="n">
-        <v>0.23180786429876</v>
+        <v>0.126322714192866</v>
       </c>
       <c r="G30" t="s">
         <v>138</v>
@@ -2552,7 +2552,7 @@
         <v>16</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>0.406145296366207</v>
       </c>
       <c r="G35" t="s">
         <v>156</v>
@@ -2639,7 +2639,7 @@
         <v>16</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>0.208270945862351</v>
       </c>
       <c r="G38" t="s">
         <v>167</v>
@@ -2772,7 +2772,7 @@
         <v>185</v>
       </c>
       <c r="B43" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C43" t="s">
         <v>186</v>
@@ -2781,45 +2781,45 @@
         <v>1</v>
       </c>
       <c r="E43" t="s">
+        <v>16</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.0766185991760893</v>
+      </c>
+      <c r="G43" t="s">
         <v>187</v>
       </c>
-      <c r="F43" t="n">
-        <v>0.382186556584935</v>
-      </c>
-      <c r="G43" t="s">
+      <c r="H43" t="n">
+        <v>0.208270945862351</v>
+      </c>
+      <c r="I43" t="s">
         <v>188</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.0766185991760893</v>
-      </c>
-      <c r="I43" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>189</v>
+      </c>
+      <c r="B44" t="s">
+        <v>113</v>
+      </c>
+      <c r="C44" t="s">
         <v>190</v>
       </c>
-      <c r="B44" t="s">
-        <v>107</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="s">
         <v>191</v>
       </c>
-      <c r="D44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" t="s">
-        <v>16</v>
-      </c>
       <c r="F44" t="n">
-        <v>0.0766185991760893</v>
+        <v>0.343380738512093</v>
       </c>
       <c r="G44" t="s">
         <v>192</v>
       </c>
       <c r="H44" t="n">
-        <v>0.208270945862351</v>
+        <v>0.0766185991760893</v>
       </c>
       <c r="I44" t="s">
         <v>193</v>
@@ -3265,112 +3265,112 @@
         <v>245</v>
       </c>
       <c r="B60" t="s">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="C60" t="s">
-        <v>16</v>
+        <v>246</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" t="s">
         <v>16</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>0.290061086989989</v>
       </c>
       <c r="G60" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>0.788467781907967</v>
       </c>
       <c r="I60" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B61" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="C61" t="s">
-        <v>248</v>
+        <v>16</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>249</v>
+        <v>16</v>
       </c>
       <c r="F61" t="n">
-        <v>0.914001122512931</v>
+        <v>0</v>
       </c>
       <c r="G61" t="s">
         <v>250</v>
       </c>
       <c r="H61" t="n">
-        <v>0.914001122512931</v>
+        <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
+        <v>251</v>
+      </c>
+      <c r="B62" t="s">
+        <v>59</v>
+      </c>
+      <c r="C62" t="s">
         <v>252</v>
       </c>
-      <c r="B62" t="s">
-        <v>82</v>
-      </c>
-      <c r="C62" t="s">
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="s">
         <v>253</v>
       </c>
-      <c r="D62" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" t="s">
+      <c r="F62" t="n">
+        <v>0.914001122512931</v>
+      </c>
+      <c r="G62" t="s">
         <v>254</v>
       </c>
-      <c r="F62" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" t="s">
+      <c r="H62" t="n">
+        <v>0.914001122512931</v>
+      </c>
+      <c r="I62" t="s">
         <v>255</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.669620389113773</v>
-      </c>
-      <c r="I62" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
+        <v>256</v>
+      </c>
+      <c r="B63" t="s">
+        <v>82</v>
+      </c>
+      <c r="C63" t="s">
         <v>257</v>
       </c>
-      <c r="B63" t="s">
-        <v>101</v>
-      </c>
-      <c r="C63" t="s">
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="s">
         <v>258</v>
       </c>
-      <c r="D63" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" t="s">
-        <v>16</v>
-      </c>
       <c r="F63" t="n">
-        <v>0.290061086989989</v>
+        <v>1</v>
       </c>
       <c r="G63" t="s">
         <v>259</v>
       </c>
       <c r="H63" t="n">
-        <v>0.478229883922796</v>
+        <v>0.669620389113773</v>
       </c>
       <c r="I63" t="s">
         <v>260</v>
@@ -3990,54 +3990,54 @@
         <v>330</v>
       </c>
       <c r="B85" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C85" t="s">
+        <v>16</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="s">
         <v>331</v>
       </c>
-      <c r="D85" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" t="s">
-        <v>332</v>
-      </c>
       <c r="F85" t="n">
-        <v>0.478229883922796</v>
+        <v>0.382583907138237</v>
       </c>
       <c r="G85" t="s">
-        <v>333</v>
+        <v>16</v>
       </c>
       <c r="H85" t="n">
-        <v>0.788467781907967</v>
+        <v>0.232048869591992</v>
       </c>
       <c r="I85" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
+        <v>332</v>
+      </c>
+      <c r="B86" t="s">
+        <v>101</v>
+      </c>
+      <c r="C86" t="s">
+        <v>333</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="s">
+        <v>334</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.478229883922796</v>
+      </c>
+      <c r="G86" t="s">
         <v>335</v>
       </c>
-      <c r="B86" t="s">
-        <v>107</v>
-      </c>
-      <c r="C86" t="s">
-        <v>16</v>
-      </c>
-      <c r="D86" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" t="s">
-        <v>336</v>
-      </c>
-      <c r="F86" t="n">
-        <v>0.382583907138237</v>
-      </c>
-      <c r="G86" t="s">
-        <v>16</v>
-      </c>
       <c r="H86" t="n">
-        <v>0.232048869591992</v>
+        <v>0.478229883922796</v>
       </c>
       <c r="I86" t="s">
         <v>336</v>
@@ -4060,7 +4060,7 @@
         <v>16</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>0.334810194556887</v>
       </c>
       <c r="G87" t="s">
         <v>338</v>
@@ -4251,25 +4251,25 @@
         <v>356</v>
       </c>
       <c r="B94" t="s">
-        <v>277</v>
+        <v>230</v>
       </c>
       <c r="C94" t="s">
-        <v>16</v>
+        <v>357</v>
       </c>
       <c r="D94" t="n">
         <v>1</v>
       </c>
       <c r="E94" t="s">
-        <v>357</v>
+        <v>16</v>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="G94" t="s">
         <v>16</v>
       </c>
       <c r="H94" t="n">
-        <v>0.334810194556887</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="I94" t="s">
         <v>357</v>
@@ -4280,25 +4280,25 @@
         <v>358</v>
       </c>
       <c r="B95" t="s">
-        <v>230</v>
+        <v>277</v>
       </c>
       <c r="C95" t="s">
+        <v>16</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" t="s">
         <v>359</v>
       </c>
-      <c r="D95" t="n">
-        <v>1</v>
-      </c>
-      <c r="E95" t="s">
-        <v>16</v>
-      </c>
       <c r="F95" t="n">
-        <v>0.755081337596291</v>
+        <v>0.910108467846823</v>
       </c>
       <c r="G95" t="s">
         <v>16</v>
       </c>
       <c r="H95" t="n">
-        <v>0.755081337596291</v>
+        <v>0.334810194556887</v>
       </c>
       <c r="I95" t="s">
         <v>359</v>
@@ -4350,7 +4350,7 @@
         <v>16</v>
       </c>
       <c r="F97" t="n">
-        <v>0.74529489290339</v>
+        <v>0.669620389113773</v>
       </c>
       <c r="G97" t="s">
         <v>16</v>
@@ -4773,7 +4773,7 @@
         <v>16</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="G112" t="s">
         <v>16</v>
@@ -4802,7 +4802,7 @@
         <v>16</v>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="G113" t="s">
         <v>16</v>
@@ -4819,7 +4819,7 @@
         <v>384</v>
       </c>
       <c r="B114" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C114" t="s">
         <v>16</v>
@@ -4831,13 +4831,13 @@
         <v>16</v>
       </c>
       <c r="F114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" t="s">
+        <v>16</v>
+      </c>
+      <c r="H114" t="n">
         <v>0.755081337596291</v>
-      </c>
-      <c r="G114" t="s">
-        <v>16</v>
-      </c>
-      <c r="H114" t="n">
-        <v>1</v>
       </c>
       <c r="I114" t="s">
         <v>16</v>
@@ -4845,11 +4845,11 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
+        <v>385</v>
+      </c>
+      <c r="B115" t="s">
         <v>386</v>
       </c>
-      <c r="B115" t="s">
-        <v>381</v>
-      </c>
       <c r="C115" t="s">
         <v>16</v>
       </c>
@@ -4866,7 +4866,7 @@
         <v>16</v>
       </c>
       <c r="H115" t="n">
-        <v>0.755081337596291</v>
+        <v>1</v>
       </c>
       <c r="I115" t="s">
         <v>16</v>
@@ -5005,7 +5005,7 @@
         <v>16</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>0.203072648183104</v>
       </c>
       <c r="G120" t="s">
         <v>16</v>
@@ -5063,7 +5063,7 @@
         <v>16</v>
       </c>
       <c r="F122" t="n">
-        <v>0.755081337596291</v>
+        <v>0.552008689413187</v>
       </c>
       <c r="G122" t="s">
         <v>16</v>
@@ -5080,7 +5080,7 @@
         <v>396</v>
       </c>
       <c r="B123" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C123" t="s">
         <v>16</v>
